--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.38398159777658</v>
+        <v>7.374897009638695</v>
       </c>
       <c r="D2" t="n">
-        <v>10.92016483392078</v>
+        <v>1.774526785512127</v>
       </c>
       <c r="E2" t="n">
-        <v>17.27599494569384</v>
+        <v>2.807349178675249</v>
       </c>
       <c r="F2" t="n">
-        <v>5.004588540066771</v>
+        <v>0.8132456377608503</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.09732047001068</v>
+        <v>3.428314576376735</v>
       </c>
       <c r="D3" t="n">
-        <v>1.216201175441498</v>
+        <v>0.1976326910092434</v>
       </c>
       <c r="E3" t="n">
-        <v>17.27599494569384</v>
+        <v>2.807349178675249</v>
       </c>
       <c r="F3" t="n">
-        <v>5.004588540066771</v>
+        <v>0.8132456377608503</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.25212508274991</v>
+        <v>10.27847032594686</v>
       </c>
       <c r="D4" t="n">
-        <v>12.55520050391293</v>
+        <v>2.040220081885852</v>
       </c>
       <c r="E4" t="n">
-        <v>17.27599494569384</v>
+        <v>2.807349178675249</v>
       </c>
       <c r="F4" t="n">
-        <v>5.004588540066771</v>
+        <v>0.8132456377608503</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
